--- a/Data/EC/NIT-9004754844.xlsx
+++ b/Data/EC/NIT-9004754844.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/701bc9d4a22bb000/Desktop/MACROS/2- MACRO COMFENALCO CARTAGENA ACTUALIZACION/Estados De Cuenta/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAAC7C2D-95A1-4D1D-B4A2-862313805F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E70CA3EA-FC23-43E8-98A2-E813F50542EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{69FEF503-42CF-40ED-8827-AE317E675EF0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F17547BB-22F1-4C23-97A9-3C5A02DB505C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="77">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,153 +71,153 @@
     <t>CAMILO CONTRERAS HEREDIA</t>
   </si>
   <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
     <t>2206</t>
   </si>
   <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
     <t>1051736967</t>
   </si>
   <si>
@@ -227,33 +227,6 @@
     <t>2404</t>
   </si>
   <si>
-    <t>1042002891</t>
-  </si>
-  <si>
-    <t>CARMELO VENEGAS RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>1235042499</t>
-  </si>
-  <si>
-    <t>YOMAIRA CERVANTES LLERENA</t>
-  </si>
-  <si>
-    <t>2510</t>
-  </si>
-  <si>
-    <t>2509</t>
-  </si>
-  <si>
-    <t>1002250389</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO TANGARIFE BLANCO</t>
-  </si>
-  <si>
-    <t>2508</t>
-  </si>
-  <si>
     <t>1051655441</t>
   </si>
   <si>
@@ -261,18 +234,6 @@
   </si>
   <si>
     <t>2410</t>
-  </si>
-  <si>
-    <t>1029144372</t>
-  </si>
-  <si>
-    <t>ZAMARA PEREZ GRANDA</t>
-  </si>
-  <si>
-    <t>2512</t>
-  </si>
-  <si>
-    <t>2511</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -371,7 +332,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -384,9 +347,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -580,29 +541,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -621,29 +582,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -681,22 +632,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>717113</xdr:colOff>
+      <xdr:colOff>667900</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>75000</xdr:rowOff>
+      <xdr:rowOff>62300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>435413</xdr:colOff>
+      <xdr:colOff>430650</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>115500</xdr:rowOff>
+      <xdr:rowOff>121850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEB01F90-BAA2-B4DC-405B-F34F324759C8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{859A89C6-364B-DA43-A855-1D527CFC36B3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -718,7 +669,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="964763" y="265500"/>
+          <a:off x="921900" y="246450"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1047,75 +998,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69306A67-B452-480A-B486-0E6408C5D8EB}">
-  <dimension ref="B2:J80"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B8DF0E9-448B-4D9A-ABAD-EA417A9D295B}">
+  <dimension ref="B2:J72"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="3"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="28"/>
+      <c r="D2" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="28"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="28"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="3"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-    </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C5" s="28"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+    </row>
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="29"/>
+      <c r="D7" s="27"/>
       <c r="E7" s="6" t="s">
         <v>7</v>
       </c>
@@ -1125,13 +1076,13 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="29"/>
+      <c r="D9" s="27"/>
       <c r="E9" s="6">
         <v>9004754844</v>
       </c>
@@ -1141,15 +1092,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="29"/>
+      <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>4535265</v>
+        <v>4125155</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1157,27 +1108,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F13" s="5">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1197,16 +1148,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1216,20 +1167,20 @@
       <c r="D16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G16" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F16" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G16" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1239,20 +1190,20 @@
       <c r="D17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G17" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F17" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G17" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1262,20 +1213,20 @@
       <c r="D18" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G18" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F18" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G18" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1285,20 +1236,20 @@
       <c r="D19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G19" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F19" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G19" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1308,20 +1259,20 @@
       <c r="D20" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G20" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F20" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G20" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1331,20 +1282,20 @@
       <c r="D21" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G21" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F21" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G21" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1354,20 +1305,20 @@
       <c r="D22" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G22" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F22" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G22" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1377,20 +1328,20 @@
       <c r="D23" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G23" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F23" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G23" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1400,20 +1351,20 @@
       <c r="D24" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G24" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F24" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G24" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1423,20 +1374,20 @@
       <c r="D25" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G25" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F25" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G25" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1446,20 +1397,20 @@
       <c r="D26" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G26" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F26" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G26" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1469,20 +1420,20 @@
       <c r="D27" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G27" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="21"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F27" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G27" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1492,20 +1443,20 @@
       <c r="D28" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G28" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="21"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F28" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G28" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1515,20 +1466,20 @@
       <c r="D29" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G29" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="21"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F29" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G29" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1538,20 +1489,20 @@
       <c r="D30" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G30" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="21"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F30" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G30" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1561,20 +1512,20 @@
       <c r="D31" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F31" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G31" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="21"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F31" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G31" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1584,20 +1535,20 @@
       <c r="D32" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G32" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="21"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F32" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G32" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1607,20 +1558,20 @@
       <c r="D33" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G33" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="21"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F33" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G33" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1630,20 +1581,20 @@
       <c r="D34" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G34" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="21"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F34" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G34" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1653,20 +1604,20 @@
       <c r="D35" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G35" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="21"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F35" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G35" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1676,20 +1627,20 @@
       <c r="D36" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G36" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="21"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F36" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G36" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1699,20 +1650,20 @@
       <c r="D37" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G37" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="21"/>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F37" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G37" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="20"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1722,20 +1673,20 @@
       <c r="D38" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G38" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="21"/>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F38" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G38" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1745,20 +1696,20 @@
       <c r="D39" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G39" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="21"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F39" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G39" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1768,20 +1719,20 @@
       <c r="D40" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G40" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F40" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G40" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1791,20 +1742,20 @@
       <c r="D41" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G41" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="21"/>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F41" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G41" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1814,20 +1765,20 @@
       <c r="D42" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G42" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="21"/>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F42" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G42" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1837,20 +1788,20 @@
       <c r="D43" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F43" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G43" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="21"/>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F43" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G43" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1860,20 +1811,20 @@
       <c r="D44" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F44" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G44" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="21"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F44" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G44" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1883,20 +1834,20 @@
       <c r="D45" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G45" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="21"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F45" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G45" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1906,20 +1857,20 @@
       <c r="D46" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G46" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="21"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F46" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G46" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="20"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1929,20 +1880,20 @@
       <c r="D47" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F47" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G47" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="21"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F47" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G47" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1952,20 +1903,20 @@
       <c r="D48" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F48" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G48" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="21"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F48" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G48" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="20"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1975,20 +1926,20 @@
       <c r="D49" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G49" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="21"/>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F49" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G49" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1998,20 +1949,20 @@
       <c r="D50" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F50" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G50" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="21"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F50" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G50" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2021,20 +1972,20 @@
       <c r="D51" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F51" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G51" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="21"/>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F51" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G51" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="20"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2044,20 +1995,20 @@
       <c r="D52" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E52" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F52" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G52" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="21"/>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F52" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G52" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="20"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2067,20 +2018,20 @@
       <c r="D53" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F53" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G53" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="21"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F53" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G53" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="20"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2090,20 +2041,20 @@
       <c r="D54" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="18" t="s">
+      <c r="E54" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F54" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G54" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="21"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F54" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G54" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="20"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2113,20 +2064,20 @@
       <c r="D55" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F55" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G55" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="21"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F55" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G55" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="20"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2136,20 +2087,20 @@
       <c r="D56" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="E56" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G56" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="21"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F56" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G56" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="20"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2159,20 +2110,20 @@
       <c r="D57" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F57" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G57" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="21"/>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F57" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G57" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="20"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2182,20 +2133,20 @@
       <c r="D58" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F58" s="19">
-        <v>84000</v>
-      </c>
-      <c r="G58" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="21"/>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F58" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G58" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2205,20 +2156,20 @@
       <c r="D59" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F59" s="19">
-        <v>77148</v>
-      </c>
-      <c r="G59" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="21"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F59" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G59" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="20"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2228,20 +2179,20 @@
       <c r="D60" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F60" s="19">
-        <v>77148</v>
-      </c>
-      <c r="G60" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="21"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F60" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G60" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="20"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2251,20 +2202,20 @@
       <c r="D61" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="F61" s="19">
-        <v>77148</v>
-      </c>
-      <c r="G61" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="21"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F61" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G61" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="20"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2274,20 +2225,20 @@
       <c r="D62" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F62" s="19">
-        <v>77148</v>
-      </c>
-      <c r="G62" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="21"/>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F62" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G62" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2297,20 +2248,20 @@
       <c r="D63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F63" s="19">
-        <v>77148</v>
-      </c>
-      <c r="G63" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="21"/>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F63" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G63" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2320,20 +2271,20 @@
       <c r="D64" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E64" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F64" s="19">
-        <v>77148</v>
-      </c>
-      <c r="G64" s="19">
-        <v>3009878</v>
-      </c>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="21"/>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F64" s="18">
+        <v>84000</v>
+      </c>
+      <c r="G64" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2343,254 +2294,70 @@
       <c r="D65" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="18">
         <v>8667</v>
       </c>
-      <c r="G65" s="19">
+      <c r="G65" s="18">
         <v>1300000</v>
       </c>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="21"/>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B66" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="16" t="s">
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="20"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B66" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="E66" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="19">
-        <v>40000</v>
-      </c>
-      <c r="G66" s="19">
-        <v>908526</v>
-      </c>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="21"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="16" t="s">
+      <c r="E66" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D67" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="F67" s="19">
-        <v>56940</v>
-      </c>
-      <c r="G67" s="19">
-        <v>1423500</v>
-      </c>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="21"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B68" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F68" s="19">
-        <v>56940</v>
-      </c>
-      <c r="G68" s="19">
-        <v>1423500</v>
-      </c>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="21"/>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F69" s="19">
-        <v>56940</v>
-      </c>
-      <c r="G69" s="19">
-        <v>1423500</v>
-      </c>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="21"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B70" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D70" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F70" s="19">
-        <v>56940</v>
-      </c>
-      <c r="G70" s="19">
-        <v>1423500</v>
-      </c>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="21"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E71" s="18" t="s">
+      <c r="F66" s="24">
+        <v>41600</v>
+      </c>
+      <c r="G66" s="24">
+        <v>1600000</v>
+      </c>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="26"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B71" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="32"/>
+      <c r="H71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B72" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="19">
-        <v>41600</v>
-      </c>
-      <c r="G71" s="19">
-        <v>1600000</v>
-      </c>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="21"/>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B72" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D72" s="17" t="s">
+      <c r="C72" s="32"/>
+      <c r="H72" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E72" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F72" s="19">
-        <v>56940</v>
-      </c>
-      <c r="G72" s="19">
-        <v>1423500</v>
-      </c>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="21"/>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B73" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D73" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E73" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="F73" s="19">
-        <v>56940</v>
-      </c>
-      <c r="G73" s="19">
-        <v>1423500</v>
-      </c>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="21"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B74" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D74" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="F74" s="26">
-        <v>28470</v>
-      </c>
-      <c r="G74" s="26">
-        <v>1423500</v>
-      </c>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="28"/>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" s="34"/>
-      <c r="H79" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B80" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C80" s="34"/>
-      <c r="H80" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="H71:J71"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>

--- a/Data/EC/NIT-9004754844.xlsx
+++ b/Data/EC/NIT-9004754844.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E70CA3EA-FC23-43E8-98A2-E813F50542EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C19D846-3089-498E-A167-D7F033F78A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F17547BB-22F1-4C23-97A9-3C5A02DB505C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5309478F-07EE-499E-AE30-CC4F3E5E6081}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="106">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -65,157 +65,178 @@
     <t>CC</t>
   </si>
   <si>
+    <t>1002413055</t>
+  </si>
+  <si>
+    <t>EDUAR FABIAN BUELVAS MEZA</t>
+  </si>
+  <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>1143339975</t>
+  </si>
+  <si>
+    <t>CAMILA ROSA DE ALBA PUELLO</t>
+  </si>
+  <si>
     <t>1047480731</t>
   </si>
   <si>
     <t>CAMILO CONTRERAS HEREDIA</t>
   </si>
   <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
     <t>1805</t>
   </si>
   <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
+    <t>1047420189</t>
+  </si>
+  <si>
+    <t>JESUS ALFREDO BANQUEZ RAMIREZ</t>
   </si>
   <si>
     <t>1051736967</t>
@@ -227,6 +248,45 @@
     <t>2404</t>
   </si>
   <si>
+    <t>1042002891</t>
+  </si>
+  <si>
+    <t>CARMELO VENEGAS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>1002188712</t>
+  </si>
+  <si>
+    <t>JHONATAN DE JESUS TORAL PAVA</t>
+  </si>
+  <si>
+    <t>1235042499</t>
+  </si>
+  <si>
+    <t>YOMAIRA CERVANTES LLERENA</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>1002250389</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO TANGARIFE BLANCO</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>1193098254</t>
+  </si>
+  <si>
+    <t>FRANCISCO JOSE CHAMORRO MOLINA</t>
+  </si>
+  <si>
     <t>1051655441</t>
   </si>
   <si>
@@ -234,6 +294,33 @@
   </si>
   <si>
     <t>2410</t>
+  </si>
+  <si>
+    <t>1043963031</t>
+  </si>
+  <si>
+    <t>ISABELLA DEL CARMEN PRENTT BERRIO</t>
+  </si>
+  <si>
+    <t>PPT</t>
+  </si>
+  <si>
+    <t>4692076</t>
+  </si>
+  <si>
+    <t>JOHANKER ANDRES MENDEZ SARMIENTO</t>
+  </si>
+  <si>
+    <t>1029144372</t>
+  </si>
+  <si>
+    <t>ZAMARA PEREZ GRANDA</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -332,9 +419,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -347,7 +432,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -547,23 +634,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -591,10 +678,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -632,22 +719,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{859A89C6-364B-DA43-A855-1D527CFC36B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAA48A93-39A7-56B1-4CF6-0349FDA87B38}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -669,7 +756,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -998,27 +1085,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B8DF0E9-448B-4D9A-ABAD-EA417A9D295B}">
-  <dimension ref="B2:J72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB321B6-692A-426B-8F40-386CC55C2E8D}">
+  <dimension ref="B2:J87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1027,7 +1114,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1038,7 +1125,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1049,7 +1136,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1060,10 +1147,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1076,8 +1163,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1092,15 +1179,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>4125155</v>
+        <v>5075022</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1108,27 +1195,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C13" s="5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F13" s="5">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1148,16 +1235,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1171,53 +1258,53 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>77148</v>
+        <v>74036</v>
       </c>
       <c r="G16" s="18">
-        <v>3009878</v>
+        <v>1850905</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="18">
-        <v>77148</v>
+        <v>74036</v>
       </c>
       <c r="G17" s="18">
-        <v>3009878</v>
+        <v>908526</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F18" s="18">
-        <v>77148</v>
+        <v>84000</v>
       </c>
       <c r="G18" s="18">
         <v>3009878</v>
@@ -1226,21 +1313,21 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F19" s="18">
-        <v>77148</v>
+        <v>84000</v>
       </c>
       <c r="G19" s="18">
         <v>3009878</v>
@@ -1249,21 +1336,21 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F20" s="18">
-        <v>77148</v>
+        <v>84000</v>
       </c>
       <c r="G20" s="18">
         <v>3009878</v>
@@ -1272,21 +1359,21 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F21" s="18">
-        <v>77148</v>
+        <v>84000</v>
       </c>
       <c r="G21" s="18">
         <v>3009878</v>
@@ -1295,18 +1382,18 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F22" s="18">
         <v>84000</v>
@@ -1318,18 +1405,18 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" s="18">
         <v>84000</v>
@@ -1341,18 +1428,18 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F24" s="18">
         <v>84000</v>
@@ -1364,18 +1451,18 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" s="18">
         <v>84000</v>
@@ -1387,18 +1474,18 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" s="18">
         <v>84000</v>
@@ -1410,18 +1497,18 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F27" s="18">
         <v>84000</v>
@@ -1433,18 +1520,18 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F28" s="18">
         <v>84000</v>
@@ -1456,18 +1543,18 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F29" s="18">
         <v>84000</v>
@@ -1479,18 +1566,18 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F30" s="18">
         <v>84000</v>
@@ -1502,18 +1589,18 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F31" s="18">
         <v>84000</v>
@@ -1525,18 +1612,18 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F32" s="18">
         <v>84000</v>
@@ -1548,18 +1635,18 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F33" s="18">
         <v>84000</v>
@@ -1571,18 +1658,18 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F34" s="18">
         <v>84000</v>
@@ -1594,18 +1681,18 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F35" s="18">
         <v>84000</v>
@@ -1617,18 +1704,18 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F36" s="18">
         <v>84000</v>
@@ -1640,18 +1727,18 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F37" s="18">
         <v>84000</v>
@@ -1663,18 +1750,18 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F38" s="18">
         <v>84000</v>
@@ -1686,18 +1773,18 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F39" s="18">
         <v>84000</v>
@@ -1709,18 +1796,18 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F40" s="18">
         <v>84000</v>
@@ -1732,18 +1819,18 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F41" s="18">
         <v>84000</v>
@@ -1755,18 +1842,18 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F42" s="18">
         <v>84000</v>
@@ -1778,18 +1865,18 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F43" s="18">
         <v>84000</v>
@@ -1801,18 +1888,18 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F44" s="18">
         <v>84000</v>
@@ -1824,18 +1911,18 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F45" s="18">
         <v>84000</v>
@@ -1847,18 +1934,18 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F46" s="18">
         <v>84000</v>
@@ -1870,18 +1957,18 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F47" s="18">
         <v>84000</v>
@@ -1893,18 +1980,18 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F48" s="18">
         <v>84000</v>
@@ -1916,18 +2003,18 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F49" s="18">
         <v>84000</v>
@@ -1939,18 +2026,18 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F50" s="18">
         <v>84000</v>
@@ -1962,18 +2049,18 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F51" s="18">
         <v>84000</v>
@@ -1985,18 +2072,18 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F52" s="18">
         <v>84000</v>
@@ -2008,18 +2095,18 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F53" s="18">
         <v>84000</v>
@@ -2031,18 +2118,18 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F54" s="18">
         <v>84000</v>
@@ -2054,18 +2141,18 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F55" s="18">
         <v>84000</v>
@@ -2077,18 +2164,18 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F56" s="18">
         <v>84000</v>
@@ -2100,18 +2187,18 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F57" s="18">
         <v>84000</v>
@@ -2123,18 +2210,18 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F58" s="18">
         <v>84000</v>
@@ -2146,18 +2233,18 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F59" s="18">
         <v>84000</v>
@@ -2169,18 +2256,18 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F60" s="18">
         <v>84000</v>
@@ -2192,21 +2279,21 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F61" s="18">
-        <v>84000</v>
+        <v>77148</v>
       </c>
       <c r="G61" s="18">
         <v>3009878</v>
@@ -2215,21 +2302,21 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F62" s="18">
-        <v>84000</v>
+        <v>77148</v>
       </c>
       <c r="G62" s="18">
         <v>3009878</v>
@@ -2238,21 +2325,21 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F63" s="18">
-        <v>84000</v>
+        <v>77148</v>
       </c>
       <c r="G63" s="18">
         <v>3009878</v>
@@ -2261,21 +2348,21 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F64" s="18">
-        <v>84000</v>
+        <v>77148</v>
       </c>
       <c r="G64" s="18">
         <v>3009878</v>
@@ -2284,80 +2371,425 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F65" s="18">
-        <v>8667</v>
+        <v>77148</v>
       </c>
       <c r="G65" s="18">
-        <v>1300000</v>
+        <v>3009878</v>
       </c>
       <c r="H65" s="19"/>
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B66" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D66" s="23" t="s">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="F66" s="18">
+        <v>77148</v>
+      </c>
+      <c r="G66" s="18">
+        <v>3009878</v>
+      </c>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="F66" s="24">
+      <c r="D67" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="18">
+        <v>138925</v>
+      </c>
+      <c r="G67" s="18">
+        <v>3473135</v>
+      </c>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="20"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F68" s="18">
+        <v>8667</v>
+      </c>
+      <c r="G68" s="18">
+        <v>1300000</v>
+      </c>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="18">
+        <v>40000</v>
+      </c>
+      <c r="G69" s="18">
+        <v>908526</v>
+      </c>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="20"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G70" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="20"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F71" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G71" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="20"/>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F72" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G72" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F73" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G73" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="20"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B74" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F74" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G74" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="20"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B75" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="18">
+        <v>68843</v>
+      </c>
+      <c r="G75" s="18">
+        <v>1721070</v>
+      </c>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F76" s="18">
         <v>41600</v>
       </c>
-      <c r="G66" s="24">
+      <c r="G76" s="18">
         <v>1600000</v>
       </c>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="26"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B71" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C71" s="32"/>
-      <c r="H71" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B72" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C72" s="32"/>
-      <c r="H72" s="1" t="s">
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B77" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G77" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="20"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G78" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="20"/>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B79" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G79" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="20"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B80" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F80" s="18">
+        <v>56940</v>
+      </c>
+      <c r="G80" s="18">
+        <v>1423500</v>
+      </c>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="20"/>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B81" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+      <c r="F81" s="24">
+        <v>28470</v>
+      </c>
+      <c r="G81" s="24">
+        <v>1423500</v>
+      </c>
+      <c r="H81" s="25"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="26"/>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B86" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" s="32"/>
+      <c r="H86" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B87" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" s="32"/>
+      <c r="H87" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="H87:J87"/>
+    <mergeCell ref="H86:J86"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
